--- a/etf_holdings/2026-08-31_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:10</t>
+          <t>2026-08-31 00:57:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:11</t>
+          <t>2026-08-31 00:57:23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:13</t>
+          <t>2026-08-31 00:57:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:14</t>
+          <t>2026-08-31 00:57:25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:14</t>
+          <t>2026-08-31 00:57:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:14</t>
+          <t>2026-08-31 00:57:25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:14</t>
+          <t>2026-08-31 00:57:25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:14</t>
+          <t>2026-08-31 00:57:25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-31_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.41%2420</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.94%753,000</t>
+          <t>8.92%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.94%</t>
+          <t>8.92%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.28%14300</t>
+          <t>-0.84%14180</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>14300</v>
+        <v>14180</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.65%80,000</t>
+          <t>5.60%80,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.65%</t>
+          <t>5.60%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+3.1%3985</t>
+          <t>-1.51%3925</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3985</v>
+        <v>3925</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.74%249,000</t>
+          <t>4.86%249,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.74%</t>
+          <t>4.86%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-1.93%3305</t>
+          <t>+6.81%3530</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+6.81%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3305</v>
+        <v>3530</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.80%228,600</t>
+          <t>3.70%228,600</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0%5490</t>
+          <t>-0.09%5485</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5490</v>
+        <v>5485</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.69%136,000</t>
+          <t>3.66%136,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.66%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+3.39%1830</t>
+          <t>+0.55%1840</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+3.39%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1830</v>
+        <v>1840</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.52%404,000</t>
+          <t>3.62%404,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.62%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-5.93%1110</t>
+          <t>-10%999</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.93%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1110</v>
+        <v>999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.27%563,000</t>
+          <t>3.06%563,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.27%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.18%540</t>
+          <t>+0.56%543</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.92%1,096,000</t>
+          <t>2.90%1,096,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.90%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.08%220.5</t>
+          <t>+9.98%242.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>220.5</v>
+        <v>242.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.71%2,416,000</t>
+          <t>2.61%2,416,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+0.4%253</t>
+          <t>-1.19%250</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.39%1,921,000</t>
+          <t>2.38%1,921,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.38%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.29%6490</t>
+          <t>-9.71%5860</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>-9.71%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6490</v>
+        <v>5860</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.28%73,000</t>
+          <t>2.32%73,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.6%3360</t>
+          <t>+1.93%3425</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3360</v>
+        <v>3425</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.21%134,000</t>
+          <t>2.20%134,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.20%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2344華邦電子</t>
+          <t>2368金像電子（股）公司</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.42%181.5</t>
+          <t>+3.1%1165</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>181.5</v>
+        <v>1165</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.10%2,293,000</t>
+          <t>2.17%393,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.17%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>2293000</v>
+        <v>393000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.23%2150</t>
+          <t>+0.7%2165</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2150</v>
+        <v>2165</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.09%197,000</t>
+          <t>2.07%197,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:21</t>
+          <t>2026-08-31 19:30:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2368金像電子（股）公司</t>
+          <t>2344華邦電子</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+9.71%1130</t>
+          <t>+0.55%182.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+9.71%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1130</v>
+        <v>182.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.99%393,000</t>
+          <t>2.04%2,293,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>393000</v>
+        <v>2293000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+2.48%5785</t>
+          <t>+3.54%5990</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>+3.54%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5785</v>
+        <v>5990</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.92%69,000</t>
+          <t>1.95%69,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6223旺矽科技</t>
+          <t>6669緯穎科技服務</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.18%5030</t>
+          <t>-1.46%7095</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5030</v>
+        <v>7095</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.81%72,000</t>
+          <t>1.83%52,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>72000</v>
+        <v>52000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+1.67%2125</t>
+          <t>-4.24%2035</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-4.24%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2125</v>
+        <v>2035</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.79%174,000</t>
+          <t>1.81%174,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6669緯穎科技服務</t>
+          <t>6223旺矽科技</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+5.65%7200</t>
+          <t>+1.99%5130</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+5.65%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>7200</v>
+        <v>5130</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.75%52,000</t>
+          <t>1.77%72,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>52000</v>
+        <v>72000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3443創意電子</t>
+          <t>2327國巨</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1.6%6015</t>
+          <t>-8.71%545</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>-8.71%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6015</v>
+        <v>545</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.72%59,000</t>
+          <t>1.74%595,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>59000</v>
+        <v>595000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6515穎崴科技</t>
+          <t>3443創意電子</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+2.38%6250</t>
+          <t>+1.41%6100</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+2.38%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6250</v>
+        <v>6100</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.65%55,000</t>
+          <t>1.74%59,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>55000</v>
+        <v>59000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2327國巨</t>
+          <t>6515穎崴科技</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+7.57%597</t>
+          <t>+0.56%6285</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+7.57%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>597</v>
+        <v>6285</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.63%595,000</t>
+          <t>1.68%55,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>595000</v>
+        <v>55000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.3%332.5</t>
+          <t>+1.8%338.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>332.5</v>
+        <v>338.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.62%987,000</t>
+          <t>1.61%987,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+2.64%621</t>
+          <t>-5.96%584</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>-5.96%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>621</v>
+        <v>584</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.57%526,000</t>
+          <t>1.60%526,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+3.11%1490</t>
+          <t>-3.69%1435</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+3.11%</t>
+          <t>-3.69%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1490</v>
+        <v>1435</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.49%209,000</t>
+          <t>1.52%209,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,25 +2034,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.01%2010</t>
+          <t>-2.49%1960</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2010</v>
+        <v>1960</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.45%148,000</t>
+          <t>1.46%148,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.94%64.4</t>
+          <t>+0.47%64.7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>64.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.42%4,525,000</t>
+          <t>1.43%4,525,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+2.12%15630</t>
+          <t>+2.78%16065</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+2.12%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>15630</v>
+        <v>16065</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.38%18,300</t>
+          <t>1.40%18,300</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+3.37%582</t>
+          <t>-5.84%548</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+3.37%</t>
+          <t>-5.84%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>582</v>
+        <v>548</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.34%482,000</t>
+          <t>1.37%482,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:23</t>
+          <t>2026-08-31 19:30:08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-4.25%1240</t>
+          <t>-0.81%1230</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-4.25%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1240</v>
+        <v>1230</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.30%203,000</t>
+          <t>1.23%203,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.52%38.75</t>
+          <t>+2.58%39.75</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+2.58%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>38.75</v>
+        <v>39.75</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.16%349</t>
+          <t>+2.58%358</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>+2.58%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.18%694,000</t>
+          <t>1.19%694,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8996高力熱處理工業</t>
+          <t>5904寶雅國際</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-3.44%1265</t>
+          <t>+1.08%75</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1265</v>
+        <v>75</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.17%181,000</t>
+          <t>1.14%3,124,500</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>181000</v>
+        <v>3124500</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5904寶雅國際</t>
+          <t>8996高力熱處理工業</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.13%74.2</t>
+          <t>-7.11%1175</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-7.11%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>74.2</v>
+        <v>1175</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.14%3,124,500</t>
+          <t>1.12%181,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>3124500</v>
+        <v>181000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.55%196</t>
+          <t>0%196</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.55%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.09%1,147,000</t>
+          <t>1.10%1,147,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.73%480.5</t>
+          <t>+4.06%500</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>+4.06%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>480.5</v>
+        <v>500</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3231緯創資通</t>
+          <t>8210勤誠興業</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.84%178</t>
+          <t>-2.12%969</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>178</v>
+        <v>969</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.92%1,041,000</t>
+          <t>0.94%193,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1041000</v>
+        <v>193000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,25 +2761,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8210勤誠興業</t>
+          <t>3231緯創資通</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+3.13%990</t>
+          <t>0%178</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>990</v>
+        <v>178</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.91%193,000</t>
+          <t>0.91%1,041,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2788,11 +2788,11 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>193000</v>
+        <v>1041000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.17%7065</t>
+          <t>+8.28%7650</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+8.28%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>7065</v>
+        <v>7650</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.89%26,000</t>
+          <t>0.90%26,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.43%707</t>
+          <t>+3.25%730</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+3.25%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>707</v>
+        <v>730</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3189景碩科技</t>
+          <t>3044健鼎科技</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.64%899</t>
+          <t>+1.33%496.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>899</v>
+        <v>496.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.83%185,000</t>
+          <t>0.83%345,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,11 +2971,11 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>185000</v>
+        <v>345000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3044健鼎科技</t>
+          <t>3189景碩科技</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+1.87%490</t>
+          <t>-8.9%819</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+1.87%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>490</v>
+        <v>819</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.82%345,000</t>
+          <t>0.81%185,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>345000</v>
+        <v>185000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+7.06%235</t>
+          <t>-2.98%228</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+7.06%</t>
+          <t>-2.98%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.70%650,000</t>
+          <t>0.75%650,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+5.39%2345</t>
+          <t>-1.71%2305</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+5.39%</t>
+          <t>-1.71%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2345</v>
+        <v>2305</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.59%54,000</t>
+          <t>0.62%54,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:24</t>
+          <t>2026-08-31 19:30:10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3529力旺電子</t>
+          <t>6831邁科科技</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-4.15%2540</t>
+          <t>-0.32%618</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-4.15%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2540</v>
+        <v>618</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.57%44,000</t>
+          <t>0.55%182,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>44000</v>
+        <v>182000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:25</t>
+          <t>2026-08-31 19:30:11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6831邁科科技</t>
+          <t>3529力旺電子</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+4.55%620</t>
+          <t>-5.51%2400</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+4.55%</t>
+          <t>-5.51%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>620</v>
+        <v>2400</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.53%182,000</t>
+          <t>0.55%44,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>182000</v>
+        <v>44000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:25</t>
+          <t>2026-08-31 19:30:11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+9.93%742</t>
+          <t>0%742</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.45%134,000</t>
+          <t>0.49%134,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:25</t>
+          <t>2026-08-31 19:30:11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+9.98%2260</t>
+          <t>-3.98%2170</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2260</v>
+        <v>2170</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.33%32,336</t>
+          <t>0.36%32,336</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:25</t>
+          <t>2026-08-31 19:30:11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,25 +3432,25 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6442光紅建聖</t>
+          <t>3533嘉澤端子工業</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+1.25%1615</t>
+          <t>-2.59%1690</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+1.25%</t>
+          <t>-2.59%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1615</v>
+        <v>1690</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.30%38,000</t>
+          <t>0.30%35,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3459,11 +3459,11 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>38000</v>
+        <v>35000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:25</t>
+          <t>2026-08-31 19:30:11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,38 +3493,38 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3533嘉澤端子工業</t>
+          <t>6442光紅建聖</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+6.77%1735</t>
+          <t>+0.93%1630</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+6.77%</t>
+          <t>+0.93%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1735</v>
+        <v>1630</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.28%35,000</t>
+          <t>0.30%38,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>35000</v>
+        <v>38000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-08-31_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:07</t>
+          <t>2026-08-31 22:22:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:08</t>
+          <t>2026-08-31 22:22:13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:10</t>
+          <t>2026-08-31 22:22:14</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:11</t>
+          <t>2026-08-31 22:22:16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:11</t>
+          <t>2026-08-31 22:22:16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:11</t>
+          <t>2026-08-31 22:22:16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:11</t>
+          <t>2026-08-31 22:22:16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:11</t>
+          <t>2026-08-31 22:22:16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
